--- a/LexIA_Diario/config/metricas_julio_2026_indicadores copy.xlsx
+++ b/LexIA_Diario/config/metricas_julio_2026_indicadores copy.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/LexIA_Diario/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_332B6FAA2C10EF4EDF9F727B2293EE2C0D091DA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94DD1415-925E-45E3-9241-494EC84317B7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resumen" sheetId="1" r:id="rId1"/>
     <sheet name="metricas_diarias" sheetId="3" r:id="rId2"/>
     <sheet name="norma_por_norma" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">norma_por_norma!$A$1:$H$94</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1385,13 +1387,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1399,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1407,7 +1409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1415,7 +1417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1423,7 +1425,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1431,7 +1433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1439,7 +1441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1447,7 +1449,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1455,7 +1457,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1463,7 +1465,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1471,7 +1473,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,7 +1481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1487,7 +1489,7 @@
         <v>0.32098765432098758</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -1495,7 +1497,7 @@
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -1503,7 +1505,7 @@
         <v>0.43697478991596639</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1511,7 +1513,7 @@
         <v>0.3708898944193062</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1519,7 +1521,7 @@
         <v>0.60277777777777775</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1535,9 +1537,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1575,7 +1577,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1613,7 +1615,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1651,7 +1653,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -1689,7 +1691,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1727,7 +1729,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1765,7 +1767,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1800,7 +1802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1829,7 +1831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1867,7 +1869,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -1905,7 +1907,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1934,7 +1936,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -1963,7 +1965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -1992,7 +1994,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -2021,7 +2023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -2059,7 +2061,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -2097,7 +2099,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2132,7 +2134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -2167,7 +2169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -2196,7 +2198,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -2225,7 +2227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2263,7 +2265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -2292,7 +2294,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2327,7 +2329,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2365,7 +2367,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2400,7 +2402,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -2438,7 +2440,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -2467,7 +2469,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -2496,7 +2498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -2525,7 +2527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2557,7 +2559,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2593,20 +2595,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="255.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -2641,7 +2644,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2664,7 +2667,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2690,7 +2693,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2725,7 +2728,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2760,7 +2763,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2795,7 +2798,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2830,7 +2833,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2853,7 +2856,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -2879,7 +2882,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -2905,7 +2908,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -2940,7 +2943,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3010,7 +3013,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3045,7 +3048,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -3071,7 +3074,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -3097,7 +3100,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -3132,7 +3135,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -3167,7 +3170,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3202,7 +3205,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3289,7 +3292,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3315,7 +3318,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -3376,7 +3379,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3399,7 +3402,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3451,7 +3454,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3477,7 +3480,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3503,7 +3506,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3529,7 +3532,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -3555,7 +3558,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -3590,7 +3593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -3642,7 +3645,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -3694,7 +3697,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -3729,7 +3732,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -3787,7 +3790,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3857,7 +3860,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -3883,7 +3886,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -3909,7 +3912,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -3935,7 +3938,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3961,7 +3964,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -3987,7 +3990,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>20</v>
       </c>
@@ -4013,7 +4016,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -4039,7 +4042,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -4065,7 +4068,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -4091,7 +4094,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -4117,7 +4120,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -4143,7 +4146,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -4169,7 +4172,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -4195,7 +4198,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -4221,7 +4224,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -4247,7 +4250,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -4273,7 +4276,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -4299,7 +4302,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>20</v>
       </c>
@@ -4325,7 +4328,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -4351,7 +4354,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -4377,7 +4380,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>20</v>
       </c>
@@ -4403,7 +4406,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>20</v>
       </c>
@@ -4429,7 +4432,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -4455,7 +4458,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -4481,7 +4484,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>20</v>
       </c>
@@ -4507,7 +4510,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -4542,7 +4545,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -4565,7 +4568,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -4588,7 +4591,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -4640,7 +4643,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>49</v>
       </c>
@@ -4663,7 +4666,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>49</v>
       </c>
@@ -4689,7 +4692,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>49</v>
       </c>
@@ -4715,7 +4718,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>52</v>
       </c>
@@ -4738,7 +4741,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>52</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>52</v>
       </c>
@@ -4799,7 +4802,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>54</v>
       </c>
@@ -4822,7 +4825,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>54</v>
       </c>
@@ -4848,7 +4851,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>54</v>
       </c>
@@ -4874,7 +4877,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -4900,7 +4903,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -4926,7 +4929,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>55</v>
       </c>
@@ -4952,7 +4955,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>55</v>
       </c>
@@ -4987,7 +4990,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>55</v>
       </c>
@@ -5022,7 +5025,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>55</v>
       </c>
@@ -5057,7 +5060,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>55</v>
       </c>
@@ -5092,7 +5095,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>56</v>
       </c>
@@ -5115,7 +5118,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>56</v>
       </c>
@@ -5138,7 +5141,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>56</v>
       </c>
@@ -5164,7 +5167,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>57</v>
       </c>
@@ -5199,7 +5202,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>57</v>
       </c>
@@ -5234,7 +5237,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -5258,6 +5261,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H94" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="FP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/LexIA_Diario/config/metricas_julio_2026_indicadores copy.xlsx
+++ b/LexIA_Diario/config/metricas_julio_2026_indicadores copy.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/LexIA_Diario/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_52EDFE20C27EAD42009F22C83E6CA2465CC25F2C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +21,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">norma_por_norma!$A$1:$H$94</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -86,91 +92,91 @@
     <t>macro_f1</t>
   </si>
   <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>analista_si</t>
+  </si>
+  <si>
+    <t>analista_rows</t>
+  </si>
+  <si>
+    <t>ia_si</t>
+  </si>
+  <si>
+    <t>tp</t>
+  </si>
+  <si>
+    <t>fp</t>
+  </si>
+  <si>
+    <t>fn</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>filas_reporte</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>sin_validacion</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
     <t>2026-07-15</t>
   </si>
   <si>
     <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>analista_si</t>
-  </si>
-  <si>
-    <t>analista_rows</t>
-  </si>
-  <si>
-    <t>ia_si</t>
-  </si>
-  <si>
-    <t>tp</t>
-  </si>
-  <si>
-    <t>fp</t>
-  </si>
-  <si>
-    <t>fn</t>
-  </si>
-  <si>
-    <t>precision</t>
-  </si>
-  <si>
-    <t>recall</t>
-  </si>
-  <si>
-    <t>f1</t>
-  </si>
-  <si>
-    <t>filas_reporte</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>sin_validacion</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
   </si>
   <si>
     <t>2026-07-17</t>
@@ -1037,7 +1043,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1387,13 +1393,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1409,7 +1415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1417,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1425,7 +1431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1433,7 +1439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1457,7 +1463,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,7 +1471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1473,7 +1479,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1481,7 +1487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1489,7 +1495,7 @@
         <v>0.32098765432098758</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -1497,7 +1503,7 @@
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -1505,7 +1511,7 @@
         <v>0.43697478991596639</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1513,7 +1519,7 @@
         <v>0.3708898944193062</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1521,7 +1527,7 @@
         <v>0.60277777777777775</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1537,52 +1543,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1615,12 +1621,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -1653,12 +1659,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1691,12 +1697,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1729,12 +1735,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1767,12 +1773,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1802,12 +1808,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1831,12 +1837,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1869,12 +1875,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1907,12 +1913,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1936,12 +1942,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1965,12 +1971,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1994,12 +2000,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2023,12 +2029,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -2061,12 +2067,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2099,12 +2105,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2134,12 +2140,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2169,12 +2175,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2198,12 +2204,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2227,12 +2233,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2265,12 +2271,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2294,12 +2300,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2329,12 +2335,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -2367,12 +2373,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2402,12 +2408,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2440,12 +2446,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2469,12 +2475,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2498,12 +2504,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2527,12 +2533,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2559,12 +2565,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2597,21 +2603,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="255.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>62</v>
@@ -2644,7 +2650,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" hidden="1">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2667,7 +2673,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2693,7 +2699,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" hidden="1">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2728,7 +2734,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" hidden="1">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2763,7 +2769,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" hidden="1">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2798,7 +2804,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" hidden="1">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2833,9 +2839,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" hidden="1">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
@@ -2856,9 +2862,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
         <v>78</v>
@@ -2882,9 +2888,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
@@ -2908,9 +2914,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" hidden="1">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
@@ -2943,9 +2949,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" hidden="1">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
@@ -2978,9 +2984,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" hidden="1">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>85</v>
@@ -3013,9 +3019,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" hidden="1">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
@@ -3048,9 +3054,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>78</v>
@@ -3074,9 +3080,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
         <v>78</v>
@@ -3100,9 +3106,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
@@ -3135,9 +3141,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" hidden="1">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>85</v>
@@ -3170,9 +3176,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
         <v>85</v>
@@ -3205,9 +3211,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>78</v>
@@ -3231,9 +3237,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
         <v>78</v>
@@ -3257,9 +3263,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>85</v>
@@ -3292,9 +3298,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
         <v>78</v>
@@ -3318,9 +3324,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
         <v>78</v>
@@ -3344,9 +3350,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" hidden="1">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
@@ -3379,9 +3385,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
         <v>72</v>
@@ -3402,9 +3408,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
         <v>78</v>
@@ -3428,9 +3434,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
         <v>78</v>
@@ -3454,9 +3460,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
         <v>78</v>
@@ -3480,9 +3486,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
         <v>78</v>
@@ -3506,9 +3512,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
         <v>78</v>
@@ -3532,9 +3538,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
         <v>78</v>
@@ -3558,9 +3564,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" hidden="1">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>85</v>
@@ -3593,9 +3599,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
         <v>78</v>
@@ -3619,9 +3625,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
         <v>78</v>
@@ -3645,9 +3651,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
         <v>78</v>
@@ -3671,9 +3677,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
         <v>78</v>
@@ -3697,9 +3703,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" hidden="1">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>85</v>
@@ -3732,9 +3738,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" hidden="1">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>72</v>
@@ -3755,9 +3761,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" hidden="1">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
         <v>85</v>
@@ -3790,9 +3796,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" hidden="1">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>85</v>
@@ -3825,9 +3831,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" hidden="1">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
         <v>85</v>
@@ -3860,9 +3866,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
         <v>78</v>
@@ -3886,9 +3892,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
@@ -3912,9 +3918,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -3938,9 +3944,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
@@ -3964,9 +3970,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
         <v>78</v>
@@ -3990,9 +3996,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>78</v>
@@ -4016,9 +4022,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
         <v>78</v>
@@ -4042,9 +4048,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
         <v>78</v>
@@ -4068,9 +4074,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
         <v>78</v>
@@ -4094,9 +4100,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
         <v>78</v>
@@ -4120,9 +4126,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
         <v>78</v>
@@ -4146,9 +4152,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
         <v>78</v>
@@ -4172,9 +4178,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
         <v>78</v>
@@ -4198,9 +4204,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
         <v>78</v>
@@ -4224,9 +4230,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B57" t="s">
         <v>78</v>
@@ -4250,9 +4256,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
         <v>78</v>
@@ -4276,9 +4282,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
         <v>78</v>
@@ -4302,9 +4308,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
         <v>78</v>
@@ -4328,9 +4334,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
@@ -4354,9 +4360,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
         <v>78</v>
@@ -4380,9 +4386,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
         <v>78</v>
@@ -4406,9 +4412,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B64" t="s">
         <v>78</v>
@@ -4432,9 +4438,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B65" t="s">
         <v>78</v>
@@ -4458,9 +4464,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
         <v>78</v>
@@ -4484,9 +4490,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
         <v>78</v>
@@ -4510,9 +4516,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B68" t="s">
         <v>85</v>
@@ -4545,9 +4551,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
         <v>72</v>
@@ -4568,9 +4574,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B70" t="s">
         <v>72</v>
@@ -4591,9 +4597,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B71" t="s">
         <v>78</v>
@@ -4617,9 +4623,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B72" t="s">
         <v>78</v>
@@ -4643,7 +4649,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" t="s">
         <v>49</v>
       </c>
@@ -4666,7 +4672,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>49</v>
       </c>
@@ -4692,7 +4698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
         <v>49</v>
       </c>
@@ -4718,7 +4724,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" t="s">
         <v>52</v>
       </c>
@@ -4741,7 +4747,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
         <v>52</v>
       </c>
@@ -4767,7 +4773,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" hidden="1">
       <c r="A78" t="s">
         <v>52</v>
       </c>
@@ -4802,7 +4808,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" hidden="1">
       <c r="A79" t="s">
         <v>54</v>
       </c>
@@ -4825,7 +4831,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
         <v>54</v>
       </c>
@@ -4851,7 +4857,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>54</v>
       </c>
@@ -4877,7 +4883,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -4903,7 +4909,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -4929,7 +4935,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>55</v>
       </c>
@@ -4955,7 +4961,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" t="s">
         <v>55</v>
       </c>
@@ -4990,7 +4996,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" t="s">
         <v>55</v>
       </c>
@@ -5025,7 +5031,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" t="s">
         <v>55</v>
       </c>
@@ -5060,7 +5066,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" hidden="1">
       <c r="A88" t="s">
         <v>55</v>
       </c>
@@ -5095,7 +5101,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" hidden="1">
       <c r="A89" t="s">
         <v>56</v>
       </c>
@@ -5118,7 +5124,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" hidden="1">
       <c r="A90" t="s">
         <v>56</v>
       </c>
@@ -5141,7 +5147,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
         <v>56</v>
       </c>
@@ -5167,7 +5173,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" hidden="1">
       <c r="A92" t="s">
         <v>57</v>
       </c>
@@ -5202,7 +5208,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" hidden="1">
       <c r="A93" t="s">
         <v>57</v>
       </c>
@@ -5237,7 +5243,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" hidden="1">
       <c r="A94" t="s">
         <v>61</v>
       </c>
